--- a/results/Int All Data -0.4/Linea_fi_explain.xlsx
+++ b/results/Int All Data -0.4/Linea_fi_explain.xlsx
@@ -1715,7 +1715,7 @@
         <v>0.002203655987694542</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.00175745011713631</v>
+        <v>-0.001751317029126496</v>
       </c>
       <c r="P3" t="n">
         <v>0.005735664654275896</v>
@@ -1751,7 +1751,7 @@
         <v>0.002958850572733969</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0002447582425324947</v>
+        <v>0.0002479009200937775</v>
       </c>
       <c r="AB3" t="n">
         <v>9.904100666080384e-05</v>
@@ -1781,7 +1781,7 @@
         <v>0.02033210178093108</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.02541826314529245</v>
+        <v>0.02540877547925829</v>
       </c>
       <c r="AL3" t="n">
         <v>0.01612728956534862</v>
@@ -1856,7 +1856,7 @@
         <v>0.09002439577859621</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.01447066692435963</v>
+        <v>0.01447378997245457</v>
       </c>
       <c r="BK3" t="n">
         <v>0.08072693975909619</v>
@@ -1883,7 +1883,7 @@
         <v>0.01522641987106103</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.002093846093283616</v>
+        <v>0.002114776574128961</v>
       </c>
       <c r="BT3" t="n">
         <v>-0.0008465949969012166</v>
@@ -1895,10 +1895,10 @@
         <v>0.003745768348290312</v>
       </c>
       <c r="BW3" t="n">
-        <v>-7.159126081234367e-05</v>
+        <v>-6.540030173717626e-05</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.006086889508348186</v>
+        <v>0.006083902650522619</v>
       </c>
       <c r="BY3" t="n">
         <v>0.001635813700686788</v>
@@ -1922,7 +1922,7 @@
         <v>-0.0001988651244189199</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.001215233974805443</v>
+        <v>0.001212247116979876</v>
       </c>
       <c r="CG3" t="n">
         <v>0.4129833990389939</v>
@@ -1958,7 +1958,7 @@
         <v>0.0847790940927233</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.1077738337933918</v>
+        <v>0.1077677614681179</v>
       </c>
       <c r="CS3" t="n">
         <v>0.3380508035193669</v>
@@ -2090,7 +2090,7 @@
         <v>0.01009248328746487</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0004986041547587695</v>
+        <v>-0.0004956235288273237</v>
       </c>
       <c r="EK3" t="n">
         <v>0.00934283400809153</v>
@@ -2184,7 +2184,7 @@
         <v>0.004035758404995827</v>
       </c>
       <c r="O4" t="n">
-        <v>0.009325744300160166</v>
+        <v>0.009331170164577945</v>
       </c>
       <c r="P4" t="n">
         <v>0.01410252142828518</v>
@@ -2220,7 +2220,7 @@
         <v>0.005311700697698365</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.00627634466018372</v>
+        <v>0.00627273592610913</v>
       </c>
       <c r="AB4" t="n">
         <v>0.0005950758544254424</v>
@@ -2250,7 +2250,7 @@
         <v>0.0154730555678994</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0229334094870301</v>
+        <v>0.02290799969030521</v>
       </c>
       <c r="AL4" t="n">
         <v>0.02204055070731448</v>
@@ -2325,7 +2325,7 @@
         <v>0.06563922404286648</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.01173938587831017</v>
+        <v>0.01174604077652812</v>
       </c>
       <c r="BK4" t="n">
         <v>0.0796851439174098</v>
@@ -2352,7 +2352,7 @@
         <v>0.0270706152526088</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.003529906127658165</v>
+        <v>0.003517879960144052</v>
       </c>
       <c r="BT4" t="n">
         <v>0.001956822858785801</v>
@@ -2364,10 +2364,10 @@
         <v>0.009627544440725465</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0003894594925720686</v>
+        <v>0.0003838346080538536</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.01498390647184583</v>
+        <v>0.01498734770919333</v>
       </c>
       <c r="BY4" t="n">
         <v>0.003980414190686451</v>
@@ -2391,7 +2391,7 @@
         <v>0.001499689937534995</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.001871935570682518</v>
+        <v>0.00186802011099054</v>
       </c>
       <c r="CG4" t="n">
         <v>0.1044661227444009</v>
@@ -2427,7 +2427,7 @@
         <v>0.06149749732615952</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.07303115064510875</v>
+        <v>0.07303899451202953</v>
       </c>
       <c r="CS4" t="n">
         <v>0.09195937425664462</v>
@@ -2559,7 +2559,7 @@
         <v>0.0209833186234661</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.009626881169975503</v>
+        <v>0.009622688260404551</v>
       </c>
       <c r="EK4" t="n">
         <v>0.02157196427190989</v>
@@ -2833,10 +2833,10 @@
         <v>-0.0157495256166983</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.00080102531239985</v>
+        <v>-0.0007689842999038521</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.00943847072879327</v>
+        <v>-0.009468339307048945</v>
       </c>
       <c r="BY5" t="n">
         <v>-0.004325536686959263</v>
@@ -3290,7 +3290,7 @@
         <v>-0.006235218182615842</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.0001792114695340407</v>
+        <v>-4.480286738351436e-05</v>
       </c>
       <c r="BT6" t="n">
         <v>-0.0006133447314748824</v>
@@ -3365,7 +3365,7 @@
         <v>0.06051637056381541</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.04080799197547139</v>
+        <v>0.04078559054177963</v>
       </c>
       <c r="CS6" t="n">
         <v>0.2562426217207042</v>
@@ -3759,7 +3759,7 @@
         <v>0.01255696004955935</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.00112945739603727</v>
+        <v>0.00111374400823086</v>
       </c>
       <c r="BT7" t="n">
         <v>-0.0002465526560074483</v>
@@ -3771,7 +3771,7 @@
         <v>0.00457720163200725</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.493428912782146e-05</v>
+        <v>2.986857825565958e-05</v>
       </c>
       <c r="BX7" t="n">
         <v>0.001883256935022193</v>
@@ -4228,7 +4228,7 @@
         <v>0.02362300252410346</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.003377763758034946</v>
+        <v>0.003400904763897334</v>
       </c>
       <c r="BT8" t="n">
         <v>0.000238974355144278</v>
@@ -4595,7 +4595,7 @@
         <v>0.05771392879450345</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.08070841239721693</v>
+        <v>0.08061353573687538</v>
       </c>
       <c r="AL9" t="n">
         <v>0.054599761051374</v>
@@ -4670,7 +4670,7 @@
         <v>0.1920417287630403</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.03697688944409747</v>
+        <v>0.03700811992504688</v>
       </c>
       <c r="BK9" t="n">
         <v>0.1884912064177723</v>
